--- a/case/A1000013.xlsx
+++ b/case/A1000013.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23152" windowHeight="11055"/>
+    <workbookView windowWidth="23040" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,13 +38,13 @@
     <t>核保</t>
   </si>
   <si>
-    <t>C:\Users\86130\Desktop\xunlianying\python\核保.yaml</t>
+    <t>D:\新框架代码\xunlianying\python\核保.yaml</t>
   </si>
   <si>
     <t>承保</t>
   </si>
   <si>
-    <t>C:\Users\86130\Desktop\xunlianying\python\承保.yaml</t>
+    <t>D:\新框架代码\xunlianying\python\承保.yaml</t>
   </si>
 </sst>
 </file>
@@ -733,13 +733,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1034,8 +1027,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="C:\Users\86130\Desktop\xunlianying\python\核保.yaml"/>
-    <hyperlink ref="B3" r:id="rId2" display="C:\Users\86130\Desktop\xunlianying\python\承保.yaml"/>
+    <hyperlink ref="B2" r:id="rId1" display="D:\新框架代码\xunlianying\python\核保.yaml"/>
+    <hyperlink ref="B3" r:id="rId2" display="D:\新框架代码\xunlianying\python\承保.yaml"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
